--- a/output/pdf_financials_xlsx/PD.xlsx
+++ b/output/pdf_financials_xlsx/PD.xlsx
@@ -2755,28 +2755,28 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>130.799</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>130.799</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>467.476</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>152.768</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>80.60599999999999</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>491.481</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>444.759</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>115.705</v>
       </c>
       <c r="K34" s="1" t="inlineStr">
         <is>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>96.626</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>74.70099999999999</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>0</v>
@@ -2879,28 +2879,28 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>130.799</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>130.799</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>467.476</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>152.768</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>80.60599999999999</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>491.481</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>444.759</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>115.705</v>
       </c>
       <c r="K36" s="1" t="inlineStr">
         <is>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>96.626</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>74.70099999999999</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>0</v>
@@ -3623,28 +3623,28 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>156.552</v>
+        <v>25.753</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>156.552</v>
+        <v>25.753</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>467.476</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>152.768</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>80.60599999999999</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>546.619</v>
+        <v>55.138</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>444.759</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>153.792</v>
+        <v>38.087</v>
       </c>
       <c r="K48" s="1" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -18817,7 +18817,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -20621,7 +20621,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -32446,7 +32446,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">

--- a/output/pdf_financials_xlsx/PD.xlsx
+++ b/output/pdf_financials_xlsx/PD.xlsx
@@ -4157,13 +4157,13 @@
         <v>0</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>4129.718</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>4608.381</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>5260.263</v>
       </c>
       <c r="H56" s="3" t="n">
         <v>0</v>
@@ -4219,13 +4219,13 @@
         <v>0</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>1187.422</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>1365.452</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>1698.529</v>
       </c>
       <c r="H57" s="3" t="n">
         <v>0</v>
@@ -4254,10 +4254,10 @@
         <v>0</v>
       </c>
       <c r="P57" s="3" t="n">
-        <v>0</v>
+        <v>35.536</v>
       </c>
       <c r="Q57" s="3" t="n">
-        <v>0</v>
+        <v>42.642</v>
       </c>
       <c r="R57" s="3" t="n">
         <v>0</v>
@@ -5069,7 +5069,7 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>12.449</v>
       </c>
       <c r="N70" s="3" t="n">
         <v>0</v>
@@ -5131,7 +5131,7 @@
         <v>0</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>12.449</v>
       </c>
       <c r="N71" s="3" t="n">
         <v>0</v>
@@ -5379,7 +5379,7 @@
         <v>7.673</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>16.591</v>
+        <v>4.142</v>
       </c>
       <c r="N75" s="3" t="n">
         <v>0</v>
@@ -5693,7 +5693,7 @@
         <v>1.095330322156544</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.9343663089420675</v>
+        <v>0.9425165899365733</v>
       </c>
       <c r="N80" s="1" t="inlineStr">
         <is>
@@ -8565,31 +8565,31 @@
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>0</v>
+        <v>1308.04</v>
       </c>
       <c r="C123" s="3" t="n">
-        <v>0</v>
+        <v>408.893</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>0</v>
+        <v>663.455</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>0</v>
+        <v>581.52</v>
       </c>
       <c r="F123" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>0</v>
+        <v>29.781</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>0</v>
+        <v>436.6</v>
       </c>
       <c r="I123" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>0</v>
+        <v>469.42</v>
       </c>
       <c r="K123" s="1" t="inlineStr">
         <is>
@@ -8705,31 +8705,31 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>-179.826</v>
+        <v>1128.214</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>-974.271</v>
+        <v>-565.378</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>-696.8630000000001</v>
+        <v>-33.408</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>-175</v>
+        <v>406.52</v>
       </c>
       <c r="F125" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>29.781</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>-30.67</v>
+        <v>405.93</v>
       </c>
       <c r="I125" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>469.42</v>
       </c>
       <c r="K125" s="1" t="inlineStr">
         <is>
@@ -11548,7 +11548,11 @@
           <t>Current portion of lease obligation (Note 13)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -40747,7 +40751,11 @@
           <t>Increase in long-term debt (Note 10)</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
@@ -42330,7 +42338,11 @@
           <t>Increase in long-term debt</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E331" s="5" t="n">
         <v>1308.04</v>
       </c>
@@ -44718,7 +44730,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E355" s="5" t="n">
         <v>31.742</v>
       </c>
@@ -54875,7 +54891,11 @@
           <t>Net earnings (loss) $</t>
         </is>
       </c>
-      <c r="D458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E458" t="inlineStr">
         <is>
           <t>-</t>
@@ -55156,7 +55176,11 @@
           <t>Net earnings (loss) $</t>
         </is>
       </c>
-      <c r="D461" t="inlineStr"/>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E461" t="inlineStr">
         <is>
           <t>-</t>
@@ -60842,7 +60866,11 @@
           <t>Net earnings (loss) 101,557</t>
         </is>
       </c>
-      <c r="D519" t="inlineStr"/>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E519" t="inlineStr">
         <is>
           <t>-</t>
